--- a/sharedata/excel/C-参数表(ParamData).xlsx
+++ b/sharedata/excel/C-参数表(ParamData).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\策划文档\配置表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ThroneOfAshes_Client\sharedata\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>参数表</t>
   </si>
@@ -76,9 +76,6 @@
     <t>hero_atk_inherit_rate</t>
   </si>
   <si>
-    <t>待配置</t>
-  </si>
-  <si>
     <t>英雄最终攻击之和转为每个上阵小兵的固定攻击加值；单个浮点系数，0.1表示10%；入场冻结</t>
   </si>
   <si>
@@ -164,6 +161,66 @@
   </si>
   <si>
     <t>宝箱每日重置时点；北京时间当日零点后秒数，21600对应6点，仅清每日开箱计数</t>
+  </si>
+  <si>
+    <t>equip_str_exp_rate</t>
+  </si>
+  <si>
+    <t>吞噬已投入培养经验的装备时（含强化等级仍为0），累计培养经验乘此继承比例；本体经验不乘此比例。单个浮点系数，取值范围0至1。</t>
+  </si>
+  <si>
+    <t>equip_str_cost</t>
+  </si>
+  <si>
+    <t>每实际吸收1点装备强化经验的金币消耗；单个整数，溢出经验不收金币。</t>
+  </si>
+  <si>
+    <t>equip_decompose_rate</t>
+  </si>
+  <si>
+    <t>已投入培养经验（含强化等级仍为0）的装备分解时，本体经验与累计培养经验合计后乘返还比例；单个浮点系数，取值范围0至1；独立于吞噬系数。</t>
+  </si>
+  <si>
+    <t>equip_exp_item</t>
+  </si>
+  <si>
+    <t>装备经验兑换返还的强化材料；填单个ItemData.id整数（由物品表中文索引映射正式ID），该物品add_equip_exp须为正整数。</t>
+  </si>
+  <si>
+    <t>equip_decompose_max</t>
+  </si>
+  <si>
+    <t>单次可分解装备的最大件数；填单个正整数。</t>
+  </si>
+  <si>
+    <t>artifact_exp_item</t>
+  </si>
+  <si>
+    <t>神器经验兑换返还材料；parm填单个ItemData.id，须对应add_artifact_exp为正整数的神器强化材料；强化溢出、转移溢出、重置共用。</t>
+  </si>
+  <si>
+    <t>artifact_transfer_cost_item</t>
+  </si>
+  <si>
+    <t>神器转移消耗物品；parm填单个ItemData.id，由物品中文索引映射正式ID；物品未配置时不默认免费。</t>
+  </si>
+  <si>
+    <t>artifact_transfer_cost_count</t>
+  </si>
+  <si>
+    <t>神器每次转移消耗的物品数量；parm填单个非负整数，对应artifact_transfer_cost_item；未定值不按0处理。</t>
+  </si>
+  <si>
+    <t>artifact_reset_cost_item</t>
+  </si>
+  <si>
+    <t>神器重置消耗物品；parm填单个ItemData.id，由物品中文索引映射正式ID；物品未配置时不默认免费。</t>
+  </si>
+  <si>
+    <t>artifact_reset_cost_count</t>
+  </si>
+  <si>
+    <t>神器每次重置消耗的物品数量；parm填单个非负整数，对应artifact_reset_cost_item；未定值不按0处理。</t>
   </si>
 </sst>
 </file>
@@ -196,6 +253,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -317,13 +381,6 @@
       <color theme="0"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-      <b/>
-      <color rgb="FFFF0000"/>
     </font>
   </fonts>
   <fills count="34">
@@ -652,153 +709,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -826,20 +883,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1430,313 +1484,313 @@
         <v>13</v>
       </c>
       <c r="C7" s="8"/>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="9">
         <v>0.1</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>15</v>
+      <c r="E7" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8"/>
       <c r="B8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="8">
         <v>1</v>
       </c>
       <c r="D9" s="8"/>
-      <c r="E9" s="9" t="s">
-        <v>19</v>
+      <c r="E9" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="8">
         <v>1</v>
       </c>
       <c r="D10" s="8"/>
-      <c r="E10" s="9" t="s">
-        <v>21</v>
+      <c r="E10" s="10" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="8">
         <v>1</v>
       </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="9" t="s">
-        <v>23</v>
+      <c r="E11" s="10" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="B12" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8">
         <v>1</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>25</v>
+      <c r="E12" s="10" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8">
         <v>1</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>27</v>
+      <c r="E13" s="10" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="B14" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="9">
+        <v>28800</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>28800</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="B15" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="8">
         <v>30</v>
       </c>
       <c r="D15" s="8"/>
-      <c r="E15" s="9" t="s">
-        <v>31</v>
+      <c r="E15" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="B16" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="8">
         <v>1</v>
       </c>
       <c r="D16" s="8"/>
-      <c r="E16" s="9" t="s">
-        <v>33</v>
+      <c r="E16" s="10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="B17" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8">
         <v>0.5</v>
       </c>
-      <c r="E17" s="9" t="s">
-        <v>35</v>
+      <c r="E17" s="10" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="B18" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" s="8">
         <v>3</v>
       </c>
       <c r="D18" s="8"/>
-      <c r="E18" s="9" t="s">
-        <v>37</v>
+      <c r="E18" s="10" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19">
         <v>10</v>
       </c>
       <c r="D19"/>
       <c r="E19" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20">
         <v>9999</v>
       </c>
       <c r="D20"/>
       <c r="E20" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21">
         <v>21600</v>
       </c>
       <c r="D21"/>
       <c r="E21" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22"/>
+      <c r="B22" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22"/>
-      <c r="B22" t="str">
-        <v>equip_str_exp_rate</v>
-      </c>
       <c r="C22"/>
-      <c r="D22" t="n" s="13">
+      <c r="D22" s="11">
         <v>0.8</v>
       </c>
-      <c r="E22" t="str" s="11">
-        <v>吞噬已投入培养经验的装备时（含强化等级仍为0），累计培养经验乘此继承比例；本体经验不乘此比例。单个浮点系数，取值范围0至1。</v>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
+      <c r="E22" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23"/>
-      <c r="B23" t="str">
-        <v>equip_str_cost</v>
-      </c>
-      <c r="C23" t="n" s="13">
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="11">
         <v>10</v>
       </c>
       <c r="D23"/>
-      <c r="E23" t="str" s="11">
-        <v>每实际吸收1点装备强化经验的金币消耗；单个整数，溢出经验不收金币。</v>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
+      <c r="E23" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24"/>
-      <c r="B24" t="str">
-        <v>equip_decompose_rate</v>
+      <c r="B24" t="s">
+        <v>47</v>
       </c>
       <c r="C24"/>
-      <c r="D24" t="n" s="13">
+      <c r="D24" s="11">
         <v>0.8</v>
       </c>
-      <c r="E24" t="str" s="11">
-        <v>已投入培养经验（含强化等级仍为0）的装备分解时，本体经验与累计培养经验合计后乘返还比例；单个浮点系数，取值范围0至1；独立于吞噬系数。</v>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
+      <c r="E24" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25"/>
-      <c r="B25" t="str">
-        <v>equip_exp_item</v>
-      </c>
-      <c r="C25" t="n" s="13">
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="11">
         <v>22001</v>
       </c>
       <c r="D25"/>
-      <c r="E25" t="str" s="11">
-        <v>装备经验兑换返还的强化材料；填单个ItemData.id整数（由物品表中文索引映射正式ID），该物品add_equip_exp须为正整数。</v>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
+      <c r="E25" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26"/>
-      <c r="B26" t="str">
-        <v>equip_decompose_max</v>
-      </c>
-      <c r="C26" t="n" s="13">
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="11">
         <v>100</v>
       </c>
       <c r="D26"/>
-      <c r="E26" t="str" s="11">
-        <v>单次可分解装备的最大件数；填单个正整数。</v>
-      </c>
-    </row>
-    <row r="27" ht="16.5" customHeight="1">
+      <c r="E26" s="12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27"/>
-      <c r="B27" t="str">
-        <v>artifact_exp_item</v>
-      </c>
-      <c r="C27" t="n" s="13">
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="11">
         <v>23001</v>
       </c>
       <c r="D27"/>
-      <c r="E27" t="str" s="11">
-        <v>神器经验兑换返还材料；parm填单个ItemData.id，须对应add_artifact_exp为正整数的神器强化材料；强化溢出、转移溢出、重置共用。</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" customHeight="1">
+      <c r="E27" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28"/>
-      <c r="B28" t="str">
-        <v>artifact_transfer_cost_item</v>
-      </c>
-      <c r="C28" t="n" s="13">
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="11">
         <v>1002</v>
       </c>
       <c r="D28"/>
-      <c r="E28" t="str" s="11">
-        <v>神器转移消耗物品；parm填单个ItemData.id，由物品中文索引映射正式ID；物品未配置时不默认免费。</v>
-      </c>
-    </row>
-    <row r="29" ht="16.5" customHeight="1">
+      <c r="E28" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29"/>
-      <c r="B29" t="str">
-        <v>artifact_transfer_cost_count</v>
-      </c>
-      <c r="C29" t="n" s="13">
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="11">
         <v>100</v>
       </c>
       <c r="D29"/>
-      <c r="E29" t="str" s="11">
-        <v>神器每次转移消耗的物品数量；parm填单个非负整数，对应artifact_transfer_cost_item；未定值不按0处理。</v>
-      </c>
-    </row>
-    <row r="30" ht="16.5" customHeight="1">
+      <c r="E29" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30"/>
-      <c r="B30" t="str">
-        <v>artifact_reset_cost_item</v>
-      </c>
-      <c r="C30" t="n" s="13">
+      <c r="B30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="11">
         <v>1002</v>
       </c>
       <c r="D30"/>
-      <c r="E30" t="str" s="11">
-        <v>神器重置消耗物品；parm填单个ItemData.id，由物品中文索引映射正式ID；物品未配置时不默认免费。</v>
-      </c>
-    </row>
-    <row r="31" ht="16.5" customHeight="1">
+      <c r="E30" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31"/>
-      <c r="B31" t="str">
-        <v>artifact_reset_cost_count</v>
-      </c>
-      <c r="C31" t="n" s="13">
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="11">
         <v>100</v>
       </c>
       <c r="D31"/>
-      <c r="E31" t="str" s="11">
-        <v>神器每次重置消耗的物品数量；parm填单个非负整数，对应artifact_reset_cost_item；未定值不按0处理。</v>
+      <c r="E31" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
